--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -256,29 +256,29 @@
 </t>
   </si>
   <si>
+    <t>Extension.id</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>Extension.id</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -338,7 +338,11 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -476,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -563,85 +567,93 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="B22" t="s" s="2">
         <v>38</v>
       </c>
     </row>
@@ -900,7 +912,7 @@
         <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s" s="2">
         <v>76</v>
@@ -911,10 +923,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -925,25 +937,25 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -994,16 +1006,16 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AJ3" t="s" s="2">
         <v>76</v>
@@ -1128,10 +1140,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
@@ -1205,10 +1217,10 @@
         <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
@@ -1236,7 +1248,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -1311,13 +1323,13 @@
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>101</v>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-clinician-user-index.xlsx
+++ b/branches/master/StructureDefinition-clinician-user-index.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
